--- a/2_Upload_Products_Chirag.xlsx
+++ b/2_Upload_Products_Chirag.xlsx
@@ -425,46 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Product Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>System ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Category Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Part Number</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Product Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Display Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -478,39 +483,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CS_MF_480_FREEFLOW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 480 FREEFLOW</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>CS_MF_480_FREEFLOW</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,39 +526,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CS_MF_540_FREEFLOW</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 540 FREEFLOW</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>CS_MF_540_FREEFLOW</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -562,39 +569,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>CS_MF_600_FREEFLOW</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 600 FREEFLOW</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>CS_MF_600_FREEFLOW</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -604,39 +612,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CS_MF_700_FREEFLOW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 700 FREEFLOW</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>CS_MF_700_FREEFLOW</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,39 +655,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>CS_MF_760_FREEFLOW</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 760 FREEFLOW</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>CS_MF_760_FREEFLOW</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -688,39 +698,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>CS_MF_550_POWERFLOW</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 550 POWERFLOW</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>CS_MF_550_POWERFLOW</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -730,39 +741,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>CS_MF_620_POWERFLOW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 620 POWERFLOW</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>CS_MF_620_POWERFLOW</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,39 +784,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>CS_MF_680_POWERFLOW</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 680 POWERFLOW</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>CS_MF_680_POWERFLOW</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -814,39 +827,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>CS_MF_770_POWERFLOW</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 770 POWERFLOW</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>CS_MF_770_POWERFLOW</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -856,39 +870,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>CS_MF_920_POWERFLOW_SUPERFLOW</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 920 POWERFLOW - SUPERFLOW</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>CS_MF_920_POWERFLOW_SUPERFLOW</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -898,39 +913,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>CS_MF_1070_POWERFLOW_SUPERFLOW</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 1070 POWERFLOW - SUPERFLOW</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>CS_MF_1070_POWERFLOW_SUPERFLOW</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -940,39 +956,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>CS_MF_1220_POWERFLOW_SUPERFLOW</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 1220 POWERFLOW - SUPERFLOW</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HEADERS</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>CS_MF_1220_POWERFLOW_SUPERFLOW</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -982,39 +999,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_7342</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA 7342</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_7342</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1024,39 +1042,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_7343</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA 7343</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_7343</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1066,39 +1085,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_7344</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA 7344</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_7344</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1108,39 +1128,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_S_7345</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA S 7345</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_S_7345</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1150,39 +1171,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_S_7345_MCS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA S 7345 MCS</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_S_7345_MCS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1192,39 +1214,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_S_7347</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA S 7347</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_S_7347</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1234,39 +1257,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>CS_MF_ACTIVA_S_7347_MCS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF ACTIVA S 7347 MCS</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>CS_MF_ACTIVA_S_7347_MCS</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1276,39 +1300,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>CS_MF_BETA_7360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF BETA 7360</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>CS_MF_BETA_7360</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1318,39 +1343,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>CS_MF_BETA_7360_PL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF BETA 7360 PL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>CS_MF_BETA_7360_PL</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1360,39 +1386,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>CS_MF_BETA_7360_PLI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF BETA 7360 PLI</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>CS_MF_BETA_7360_PLI</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1402,39 +1429,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>CS_MF_BETA_7370</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF BETA 7370</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>CS_MF_BETA_7370</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1444,39 +1472,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>CS_MF_BETA_7370_PL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF BETA 7370 PL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>CS_MF_BETA_7370_PL</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1486,39 +1515,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>CS_MF_BETA_7370_PLI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF BETA 7370 PLI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>CS_MF_COMBINE_HARVESTERS</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>CS_MF_BETA_7370_PLI</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1528,39 +1558,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>CS_MF_IDEAL_7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF IDEAL 7</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>CS_MF_IDEAL</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>CS_MF_IDEAL_7</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1570,39 +1601,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>CS_MF_IDEAL_8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF IDEAL 8</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>CS_MF_IDEAL</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>CS_MF_IDEAL_8</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1612,39 +1644,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>CS_MF_IDEAL_9</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF IDEAL 9</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>CS_MF_IDEAL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>CS_MF_IDEAL_9</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1654,39 +1687,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>CS_MF_SB_1840</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF SB 1840</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>CS_MF_SMALL_SQUARE_BALERS</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>CS_MF_SB_1840</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1696,39 +1730,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>CS_MF_SB_1842S</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF SB 1842S</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>CS_MF_SMALL_SQUARE_BALERS</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>CS_MF_SB_1842S</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1738,35 +1773,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>CS_MF_DM_164_287_FARMER</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 164-287 FARMER</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>CS_MF_DM_164_287_FARMER</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Farmer Series</t>
         </is>
@@ -1780,35 +1820,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>CS_MF_DM_246_287_ISL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 246-287 ISL</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>CS_MF_DM_246_287_ISL</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Farmer Series ISL</t>
         </is>
@@ -1822,35 +1867,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>CS_MF_DM_255_357_P</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 255-357 P</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>CS_MF_DM_255_357_P</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Rear attachment, side suspension, Pairwise</t>
         </is>
@@ -1864,35 +1914,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>CS_MF_DM_265_TL_V</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 265 TL-V</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>CS_MF_DM_265_TL_V</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Rear attachment, Three Point Vertical</t>
         </is>
@@ -1906,35 +1961,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>CS_MF_DM_306_TR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 306 TR</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>CS_MF_DM_306_TR</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Trailed With Transport Chassis</t>
         </is>
@@ -1948,35 +2008,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>CS_MF_DM_306_316_FP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 306-316 FP</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>CS_MF_DM_306_316_FP</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Front Mounted Headstock</t>
         </is>
@@ -1990,35 +2055,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>CS_MF_DM_316_FQ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 316 FQ</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>CS_MF_DM_316_FQ</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>Front Mower with 3 Dimensional</t>
         </is>
@@ -2032,35 +2102,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>CS_MF_DM_316_TL_V</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 316 TL-V</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>CS_MF_DM_316_TL_V</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Rear attachment, Three Point Vertical</t>
         </is>
@@ -2074,35 +2149,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>CS_MF_DM_367_TL_V</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 367 TL-V</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>CS_MF_DM_367_TL_V</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Rear attachment, Three Point Vertical</t>
         </is>
@@ -2116,35 +2196,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>CS_MF_DM_8612_TL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 8612 TL</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>CS_MF_DM_8612_TL</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Butterfly</t>
         </is>
@@ -2158,35 +2243,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>CS_MF_DM_9614_10114_TL_KC_RC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 9614-10114 TL KC/RC</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>CS_MF_DM_9614_10114_TL_KC_RC</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Butterfly</t>
         </is>
@@ -2200,35 +2290,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>CS_MF_DM_9614_10114_TL_KCB_RCB</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF DM 9614-10114 TL KCB/RCB</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>CS_MF_DISC_MOWERS</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>CS_MF_DM_9614_10114_TL_KCB_RCB</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Butterfly Conveyor ISO</t>
         </is>
@@ -2242,39 +2337,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>CS_MFTH_6030H</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.6030H</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>CS_MFTH_6030H</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2284,39 +2380,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>CS_MFTH_6534H</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.6534H</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>CS_MFTH_6534H</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2326,39 +2423,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>CS_MFTH_6534DCT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.6534DCT</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>CS_MFTH_6534DCT</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2368,39 +2466,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>CS_MFTH_7030H</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.7030H</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>CS_MFTH_7030H</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2410,39 +2509,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>CS_MFTH_7035H</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.7035H</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>CS_MFTH_7035H</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2452,39 +2552,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>CS_MFTH_7038H</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.7038H</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>CS_MFTH_7038H</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2494,39 +2595,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>CS_MFTH_7038DCT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.7038DCT</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>CS_MFTH_7038DCT</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2536,39 +2638,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>CS_MFTH_8043H</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.8043H</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>CS_MFTH_8043H</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2578,39 +2681,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>CS_MFTH_8043DCT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MFTH.8043DCT</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>CS_MF_TH</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>CS_MFTH_8043DCT</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2620,39 +2724,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>CS_MF_FL_3615DM</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF FL.3615DM</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>CS_MF_FRONT_LOADER_4700M_CAB</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>CS_MF_FL_3615DM</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2662,39 +2767,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>CS_MF_FL_3817DM</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF FL.3817DM</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>CS_MF_FRONT_LOADER_4700M_CAB</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>CS_MF_FL_3817DM</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2704,39 +2810,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>CS_MF_FL_3416XDM</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF FL.3416XDM</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>CS_MF_FRONT_LOADER_4700M_CAB</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>CS_MF_FL_3416XDM</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2746,35 +2853,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>CS_MF_TD_454_868_DN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF TD 454-868 DN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>CS_MF_TEDDERS</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>CS_MF_TD_454_868_DN</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>3 point linkage</t>
         </is>
@@ -2788,35 +2900,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>CS_MF_TD_776X_1110_DN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF TD 776X-1110 DN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>CS_MF_TEDDERS</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>CS_MF_TD_776X_1110_DN</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>3 Point Linkage</t>
         </is>
@@ -2830,35 +2947,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>CS_MF_TD_1028X_1310X_TRC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF TD 1028X-1310X TRC</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>CS_MF_TEDDERS</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>CS_MF_TD_1028X_1310X_TRC</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>Trailed With transp. Chassis Hook Tines</t>
         </is>
@@ -2872,35 +2994,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>CS_MF_TD_776_868_TRC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF TD 776-868 TRC</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>CS_MF_TEDDERS</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>CS_MF_TD_776_868_TRC</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Trailed, With Transport chassis</t>
         </is>
@@ -2914,39 +3041,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>CS_MF_LB_2233</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF LB 2233</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>CS_MF_LARGE_SQUARE_BALERS</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>CS_MF_LB_2233</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2956,39 +3084,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>CS_MF_LB_2224</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF LB 2224</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>CS_MF_LARGE_SQUARE_BALERS</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>CS_MF_LB_2224</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2998,39 +3127,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>CS_MF_LB_2234</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF LB 2234</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>CS_MF_LARGE_SQUARE_BALERS</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>CS_MF_LB_2234</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3040,39 +3170,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>CS_MF_LB_2244</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF LB 2244</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>CS_MF_LARGE_SQUARE_BALERS</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>CS_MF_LB_2244</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3082,39 +3213,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>CS_MF_3130_F_PROTEC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 3130 F PROTEC</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>CS_MF_3100_F_PROTEC</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>CS_MF_3130_F_PROTEC</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3124,39 +3256,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>CS_MF_4160_V_PROTEC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 4160 V PROTEC</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>CS_MF_4100_V_PROTEC</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>CS_MF_4160_V_PROTEC</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3166,39 +3299,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>CS_MF_3130_F</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF 3130 F</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>CS_MF_3100_F_ROUND_BALERS</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>CS_MF_3130_F</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3208,35 +3342,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>CS_MF_RK_662_772_SD_TRC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RK 662-772 SD TRC</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>CS_MF_RAKES</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>CS_MF_RK_662_772_SD_TRC</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>Transp. Chassis Sid. Swath delivery 2 R</t>
         </is>
@@ -3250,35 +3389,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>CS_MF_RK_662_762_862_922_1002_TRC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RK 662-762-862-922-1002 TRC</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>CS_MF_RAKES</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>CS_MF_RK_662_762_862_922_1002_TRC</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>Transp. Chassis, Side Swath delivery 2 R</t>
         </is>
@@ -3292,35 +3436,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>CS_MF_RK_842_SD_TRC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RK 842 SD TRC</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>CS_MF_RAKES</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>CS_MF_RK_842_SD_TRC</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>Transp. Chassis, Side Swath delivery 2 R</t>
         </is>
@@ -3334,35 +3483,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>CS_MF_RK_341_451_DN</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RK 341-451 DN</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>CS_MF_RAKES</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>CS_MF_RK_341_451_DN</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>Three Point Linkage, Float. Headstock</t>
         </is>
@@ -3376,35 +3530,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>CS_MF_RK_1254_TRC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RK 1254 TRC</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>CS_MF_RAKES</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>CS_MF_RK_1254_TRC</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>Trans.Chassis, Cent. Swath delivery 4 R</t>
         </is>
@@ -3418,35 +3577,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>CS_MF_RK_1404_TRC_PRO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RK 1404 TRC-PRO</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>CS_MF_RAKES</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>CS_MF_RK_1404_TRC_PRO</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>Trans. Chassis Cent.Swath delivery, 4 R</t>
         </is>
@@ -3460,39 +3624,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>CS_MF_RB_4160_V</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RB 4160 V</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>CS_MF_4100_V_ROUND_BALERS</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>CS_MF_RB_4160_V</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3502,39 +3667,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>CS_MF_RB_4180_V</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>Chirag Singhal - MF RB 4180 V</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>CS_MF_4100_V_ROUND_BALERS</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>CS_MF_RB_4180_V</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Configurable</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configurable</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Scraped Product</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
